--- a/APEX_Automotives_FPA_Model.xlsx
+++ b/APEX_Automotives_FPA_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\debas\OneDrive\Desktop\APEX Automotive-FPA-Model\APEX-Automotives-FPA-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9524645D-AFB1-4991-A031-7A0AD5791511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A164A8DB-E66F-46D9-B48F-59C0B3ED8BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{42011396-5C4E-468B-ADF2-F08F41B88F4D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42011396-5C4E-468B-ADF2-F08F41B88F4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="5" r:id="rId1"/>
